--- a/06_wine_photos/wine_photo_metadata.xlsx
+++ b/06_wine_photos/wine_photo_metadata.xlsx
@@ -343,7 +343,7 @@
     </x:row>
     <x:row r="2" ht="85" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>IMG_010842.png</x:v>
+        <x:v>IMG_010842.jpg</x:v>
       </x:c>
       <x:c r="B2" s="12" t="n">
         <x:v>46010.7975</x:v>
@@ -372,7 +372,7 @@
     </x:row>
     <x:row r="3" ht="85" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>IMG_010844.png</x:v>
+        <x:v>IMG_010844.jpg</x:v>
       </x:c>
       <x:c r="B3" s="12" t="n">
         <x:v>46010.80006944444</x:v>
@@ -401,7 +401,7 @@
     </x:row>
     <x:row r="4" ht="85" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>IMG_010847.png</x:v>
+        <x:v>IMG_010847.jpg</x:v>
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:v>46010.80668981482</x:v>
@@ -430,7 +430,7 @@
     </x:row>
     <x:row r="5" ht="85" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>IMG_010851.png</x:v>
+        <x:v>IMG_010851.jpg</x:v>
       </x:c>
       <x:c r="B5" s="12" t="n">
         <x:v>46010.81825231481</x:v>
@@ -459,7 +459,7 @@
     </x:row>
     <x:row r="6" ht="85" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>IMG_010853.png</x:v>
+        <x:v>IMG_010853.jpg</x:v>
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:v>46010.82351851852</x:v>
@@ -488,7 +488,7 @@
     </x:row>
     <x:row r="7" ht="85" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>IMG_010861.png</x:v>
+        <x:v>IMG_010861.jpg</x:v>
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:v>46010.84454861111</x:v>
@@ -517,7 +517,7 @@
     </x:row>
     <x:row r="8" ht="85" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>IMG_002184.png</x:v>
+        <x:v>IMG_002184.jpg</x:v>
       </x:c>
       <x:c r="B8" s="12" t="n">
         <x:v>44639.79619212963</x:v>
@@ -546,7 +546,7 @@
     </x:row>
     <x:row r="9" ht="85" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>IMG_002186.png</x:v>
+        <x:v>IMG_002186.jpg</x:v>
       </x:c>
       <x:c r="B9" s="12" t="n">
         <x:v>44639.79738425926</x:v>
@@ -575,7 +575,7 @@
     </x:row>
     <x:row r="10" ht="85" customHeight="1">
       <x:c r="A10" s="11" t="str">
-        <x:v>IMG_002189.png</x:v>
+        <x:v>IMG_002189.jpg</x:v>
       </x:c>
       <x:c r="B10" s="12" t="n">
         <x:v>44639.799849537034</x:v>
@@ -604,7 +604,7 @@
     </x:row>
     <x:row r="11" ht="85" customHeight="1">
       <x:c r="A11" s="11" t="str">
-        <x:v>IMG_002194.png</x:v>
+        <x:v>IMG_002194.jpg</x:v>
       </x:c>
       <x:c r="B11" s="12" t="n">
         <x:v>44639.80372685185</x:v>
@@ -633,7 +633,7 @@
     </x:row>
     <x:row r="12" ht="85" customHeight="1">
       <x:c r="A12" s="11" t="str">
-        <x:v>IMG_002203.png</x:v>
+        <x:v>IMG_002203.jpg</x:v>
       </x:c>
       <x:c r="B12" s="12" t="n">
         <x:v>44639.83678240741</x:v>
